--- a/src/attributions/attributions_ig_traj_83.xlsx
+++ b/src/attributions/attributions_ig_traj_83.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1002,184 +1002,184 @@
         <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1207136776600321</v>
+        <v>0.1065590365456706</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2423024455985499</v>
+        <v>0.1418859697106051</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005374176121488893</v>
+        <v>-0.1378174212175087</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.07541815276151176</v>
+        <v>0.09561109359600173</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2149985903168879</v>
+        <v>-0.0871645506878863</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02294959987369615</v>
+        <v>-0.1202385443268583</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
         <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1063339094882755</v>
+        <v>-0.06578689819714223</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01394680953777648</v>
+        <v>-0.09482858086873176</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.01137358646709177</v>
+        <v>0.05996962021264232</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.01658479900506774</v>
+        <v>0.00205504616370891</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.01208351808461532</v>
+        <v>0.086892235360628</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.0004440765254445339</v>
+        <v>-0.002984415637210665</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.03554061054620306</v>
+        <v>0.06021603747236549</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.04021729487905552</v>
+        <v>-0.06608335611160551</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07759915751275892</v>
+        <v>0.1843616606752985</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1767592602726039</v>
+        <v>0.2995294485125412</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.07839264346614182</v>
+        <v>-0.1004700849838145</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.0108300864088781</v>
+        <v>0.04258623749498246</v>
       </c>
       <c r="AY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.01477925423043125</v>
+        <v>-0.08685068196333237</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.09076894492908641</v>
+        <v>0.1261364971415077</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.02907409353348358</v>
+        <v>-0.1045212368931069</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
         <v>-0</v>
@@ -1188,52 +1188,52 @@
         <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0300776765823109</v>
+        <v>0.03321864249703177</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.05324375875133324</v>
+        <v>-0.02919453466741371</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.0816346210201504</v>
+        <v>0.01678639697512163</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.07852575589901419</v>
+        <v>0.04903635335396866</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.01899427025985643</v>
+        <v>-0.1688521262699059</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.02409089098383337</v>
+        <v>0.001086074265224995</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>-0</v>
@@ -1242,55 +1242,55 @@
         <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.0351828300481634</v>
+        <v>-0.1315097818916881</v>
       </c>
       <c r="CF2" t="n">
         <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.03740581133404869</v>
+        <v>-0.04952692289946237</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01959344589137578</v>
+        <v>0.001853010723370293</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>-0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.0109574491941789</v>
+        <v>-0.07041931786543794</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.02695512644018117</v>
+        <v>0.1372283982945328</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.04735313135584056</v>
+        <v>-0.04984758495759148</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
@@ -1299,19 +1299,19 @@
         <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04972248908286744</v>
+        <v>-0.1334530482476488</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.04294037083382247</v>
+        <v>-0.03829302072884615</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.01300290137226959</v>
+        <v>0.02680812957255315</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>-0</v>
@@ -1323,49 +1323,49 @@
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.03367236878889769</v>
+        <v>-0.07773551367108712</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01883731363827525</v>
+        <v>0.06819644376545948</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.04878514119211853</v>
+        <v>-0.0620110215696737</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.01724963747544638</v>
+        <v>-0.04031664532260727</v>
       </c>
       <c r="DP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.04923827118775025</v>
+        <v>-0.08114655271422785</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.01741754025609108</v>
+        <v>0.02391528362387665</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1374,25 +1374,25 @@
         <v>-0</v>
       </c>
       <c r="DV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.06232683367924737</v>
+        <v>-0.05833201976657106</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.008166624026259794</v>
+        <v>0.1136475706174347</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.03432712046390961</v>
+        <v>0.2478047900295096</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1407,22 +1407,22 @@
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.04419106693749611</v>
+        <v>-0.1211641738495524</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0938691243097028</v>
+        <v>0.1625996116804201</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.03337327474115563</v>
+        <v>0.05791763696338117</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
@@ -1434,22 +1434,22 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.05524633990337205</v>
+        <v>-0.01473242216190756</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.05458425257331163</v>
+        <v>-0.004296934602339098</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.0181611645046857</v>
+        <v>0.02803398085857489</v>
       </c>
       <c r="ET2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV2" t="n">
         <v>0</v>
@@ -1461,22 +1461,22 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.04501369381718781</v>
+        <v>-0.180843114945614</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.03439071615201791</v>
+        <v>-0.005555076117706574</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01959492007179191</v>
+        <v>0.03035776186747315</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
         <v>0</v>
@@ -1488,22 +1488,22 @@
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.01283727506370472</v>
+        <v>-0.2255914251150368</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.006750623608650416</v>
+        <v>0.06445181059499774</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.01209768093104599</v>
+        <v>0.106282784841368</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
         <v>0</v>
@@ -1512,52 +1512,52 @@
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.01474334462705824</v>
+        <v>-0.07802473783940837</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.007985635772036061</v>
+        <v>0.2895994749895927</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.00508330136040864</v>
+        <v>-0.0380394403837744</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03753255017633956</v>
+        <v>0.03897538361527338</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.02009416768528361</v>
+        <v>-0.03078247710439546</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1568,106 +1568,106 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.003298026867036885</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>-0.0001765538743912393</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.002940167429529095</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.004265217997507353</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>-0.004484535988503745</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>6.914302633340988e-05</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.0128070710653615</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.003790514414436068</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.008053200762643152</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.002373347412225993</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>-0.001455793587542306</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.00204016697844231</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1676,169 +1676,169 @@
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.005223448888468222</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.007317759387067149</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.000793135675984e-05</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.007946777924115607</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.01704112986785253</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.006725994053786882</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.006198115509983798</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.01063515918261435</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.002377760754340248</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.005311696502165765</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.008330842068277089</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0.0002603378292062514</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.01063865011191368</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.006988562333205848</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.01028284376528798</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.001695170422495447</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.004079835367736623</v>
       </c>
       <c r="CI3" t="n">
         <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.002745129920163404</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.001686264030891371</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,97 +1847,97 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.01435893871474503</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.007522391542113236</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.003567011714638517</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.006998810056018943</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.004733568874202979</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.001194248056765041</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.01177267233942642</v>
       </c>
       <c r="DJ3" t="n">
         <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.002405215535092529</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.009141364347934486</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.01692806341493835</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.002031087138518301</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,142 +1946,142 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.006496637066646362</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY3" t="n">
         <v>0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>0.001574380557938878</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.01147500498678859</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.00689729976573358</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.002163514251437577</v>
       </c>
       <c r="EK3" t="n">
         <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0.0008438225494494767</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0.001687943499624313</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.005157034492315576</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.004286841497121016</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.003679172032037607</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.008577675630059475</v>
       </c>
       <c r="FC3" t="n">
         <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.00690909066610743</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.004359014094911752</v>
       </c>
       <c r="FH3" t="n">
         <v>0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>0.006170505817179848</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>0.002992396609905865</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0.02002564393006294</v>
       </c>
       <c r="FQ3" t="n">
         <v>0</v>
@@ -2093,45 +2093,6873 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>0.004228297101386383</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0.005016704571169722</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0.004352746680674752</v>
       </c>
       <c r="FZ3" t="n">
         <v>0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
         <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.01447333191701238</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.4020999473715919</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.09847898204062344</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2038397478533458</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.3755486294520515</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1478242573183164</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1092258948511525</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.09635221931194196</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1117791481274194</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1528487191953532</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.02270234258713241</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.03765683504196828</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0178386815695622</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.264240065308484</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.2855449085438668</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.07888438326974059</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.6854586114687781</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.1458639420440582</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.17978260936975</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.03654714357706367</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.02201506886929582</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>-0.0005157713353656963</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.07772805029090749</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-0.06014636997613829</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-0.05081802714924697</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.5268458868942424</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.06458066080332366</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.2661837128095147</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.3479986819115933</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.0194988087232541</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>-0.1467629065241869</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.2716518387694417</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>-0.00886879466455924</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-0.09855652148052312</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.3483028355893977</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.03351833398826438</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>-0.1565026727502048</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.05812683663051194</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.03335144275909147</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>-0.05233006980969051</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.2019546371294227</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>-0.02753330712157557</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>-0.05636110331678371</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>-0.1478863362611105</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-0.0354669442215244</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.2935152597172195</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.2349683943203794</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.01361428350306607</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>-0.08790900611764256</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.2120614541223068</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.08457901080959576</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>-0.002469463147081997</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.3744878409794071</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.01486607322429393</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>-0.1474566825627376</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.1448715891804258</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.1015889533819583</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>-0.02692554033895533</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.3491510492259298</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.005733118324703974</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>-0.2337518524078465</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.1847726009411242</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>-0.08558519772269654</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.000604318761502058</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.004491578654933334</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.007406664283609228</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.008885442739668825</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0285358662041127</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.004371053472743914</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.007104273144836118</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.008866807892937397</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.01021836740221509</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-0.008200169352965756</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-0.003264698712794951</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-0.0004289822591846452</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.0003387346884003084</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.01885893392724037</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.007135755054550345</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.007959984404842989</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.03129971563642063</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.005557814099664111</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0.03335282617863774</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>-0.01959414215250064</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.007905556117832562</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.01732317554369999</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.021650400576877</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.01249860146975277</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.0001258584109865486</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.007831135862304935</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>-0.00433517094166415</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.005713268122128365</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.006319606668911866</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.01090817562821248</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.02731006958012347</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0.02681973607329355</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.01251958359823513</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.00883745550520163</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0.008198910113532359</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0.01042549724929736</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.003385258777210333</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0.003622653147706431</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.0005967848611938358</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0.03156074894899454</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>-0.01373911607133684</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>-0.008820137097282613</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0.00942502188753478</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>-0.0153810046004041</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>-0.0106765953527962</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0.001333194551205979</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>-0.00189377223627211</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0.009329947108877917</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>-0.01458399016993625</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>-0.01632977130441766</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>-0.002892302652554379</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>-0.0009656946296309146</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>-0.007412523563659742</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0.01242623068305415</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0.001728727152216829</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0.009926010992108462</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0.01705686101299802</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0.04018139478533323</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>-0.05481093378763318</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0.0004103937026877759</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>-0.01231357803694688</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>-0.00111632672369105</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.01333887599164624</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.02357818071182153</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.02692769376462921</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.01856177557438414</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.01529071272885671</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.01566507728361065</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-9.032075281416756e-05</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.0290682689537269</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.003955639180980634</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.007015359436993525</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.0007512505538536269</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.009853179086223011</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.03233793659311406</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.03585198891735435</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.01571609102028492</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.0513328327292754</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.06936010831478187</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.0717180191668202</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.004866335089775301</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.05582101821559865</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.04058252333777846</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.02018518967514495</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.04176149716580559</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.06161295831198204</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-0.02614323324633226</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.07170231837950712</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>-0.0130362849357569</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.02580834034378944</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.007478520930410877</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.002433983552034368</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.007613424309747979</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.04597912912636852</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.0558660292045017</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.0214091594462423</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.006325105298736592</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.009186072358899487</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.01024152473361703</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0.02243306053402092</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>-0.001473611582435525</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0.001911246350359001</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.00217201263089993</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.01833515635501547</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0.03026969298512862</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0.03450835341533972</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.01912336880925581</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>6.199800943594962e-05</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0.01246038312429486</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.007300143819874621</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0.001403047426287845</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>-0.02856580326936828</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.01781634957527692</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.01919193666445476</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0.001634429673996066</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.003689300390313763</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.02396113934720891</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>-0.003227853748444528</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>-0.03134980841464526</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>-0.0004385789836020645</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.0008096748435442873</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>-0.001743324710529435</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.01364961758051532</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0.03353711509671535</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.159305599129992</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.05061720668845721</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.05173295965589613</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.2161501144112719</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.08428967667073393</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.0490804306638512</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0828606150860265</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.04956057959808152</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.02029172122689408</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.004575091790403289</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-7.426801312040048e-11</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>-0.008029638493316475</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.0312033375804216</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.06707405878717482</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.04649490063234048</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.3598921218571787</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.1652848331263171</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.1361511389521742</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.06727086436201764</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0.03573781705948016</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.01435605966916778</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.1087425222688199</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.09923968150933384</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0.04835254518103108</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.2309095606634092</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0.06653254778399767</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>-0.02213550555538252</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0.06449569160151281</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.04635871278807326</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.01374749414349384</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0.1062315095656951</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.1032873935357417</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>-0.009393330064740999</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-0.0568303269290778</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0.02500675357497247</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0.02132593534807927</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-0.04908793517037255</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0.000349418508853985</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>-0.006210200241368499</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0.0007441534141456452</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0.03446612784129031</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>-0.016011625325138</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0.08240622755244592</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>-0.1129059823330154</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>-0.02389636592369845</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0.01471976046127074</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0.01803077557272067</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0.0004266806596881781</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0.007345243305825746</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0.09410735444202306</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0.02201490239908797</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0.07749520043322999</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0.02611016744698695</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0.00805559647326747</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0.0455455256896739</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0.09897656010328473</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0.00941022120364016</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0.01568610604561834</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0.03130209622261052</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>-0.02402568746203606</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>-0.06541462757934222</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0.0516287560644766</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2261075293136231</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.09376400688984216</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01704259363440407</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2570943641887197</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.1134720464415101</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.00224246660314808</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.0660102710809737</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.04541581400101093</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.0439126509478452</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.01226458571968061</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-6.898363665641636e-11</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.003074097790906856</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.08016159073981838</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.0612352100970424</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.05142999467881537</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.2412142718859949</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.07222091430296883</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.05031672392608644</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.01501594954457613</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.0451537386002456</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.0402135165770573</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.003210331149140333</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-0.01740715340206427</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.03994340529074219</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.1705146783649493</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.06028279203073254</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.015038428482473</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.08148019526191232</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.06257785947610729</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-0.01592809499528591</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.055653608400931</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.1221110427449337</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.03591934643625753</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.0753987268959378</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.06693990168786179</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>-0.009786937857846531</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.07369491997755873</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.0122534694569378</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0.05103095517288665</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.04814927348217235</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.04256518162190326</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.01577285101648205</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.02800555862977924</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>-0.04076988527629436</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.05121324244938549</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.06456603695088504</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.04503832862911034</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.0008577059207353697</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.01377520527713494</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.002929388337159034</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.007474581936739799</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.09104375545348001</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.071641420163072</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.01999892221917839</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.06860887422368875</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.05627417812927504</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.003131894957826671</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.001527147061564477</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.0299357579605026</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>-0.01351505887585383</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.07705221674623813</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.02276564292005548</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2551306003850013</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.0002223846243961382</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.06921926705526828</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3513495162734956</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.06209487453500866</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.05307849296937248</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.04387191101359333</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.04728430843889152</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.006412580328025797</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.007633081957704544</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.02739472520789605</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.01606060195331093</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.0388363926413611</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.0269775583447891</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.02417549375554442</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.2760782498809413</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.1020596867446193</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.05034135657395987</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.02759269347889571</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.03631757103252736</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0.04715832984164987</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.02412977034737123</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.0543633764353389</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-0.001065841895661275</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.2019660274357478</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.01258034228497258</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-0.03159367469527731</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0.08926813645889678</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.00346214527610709</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.04873114928994303</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0.1205322016584415</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.05477577962376338</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.03905045170184394</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-0.09194686672040708</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.006718762381446489</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.04473090039552029</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0.04024204734849957</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0.117927582379644</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.02383060141716009</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0.08982621927630091</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.04868900749347436</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>-0.01280446850736821</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>-0.0111114327475031</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.08091562536864848</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>-0.1010737951097037</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0.01598840786002705</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0.03821743726232164</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.02634459893711695</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0.004868531294077398</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.06758742744942543</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.04786935608988209</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0.1026053228078844</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0.01510941156715961</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.03939253193113165</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0.1291580949756714</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.08826182743091061</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>-2.718746477522102e-05</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.0008711082965575929</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0.004570636632830575</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>-0.03264314088480078</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>-0.01801834953708252</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.0120648597293158</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2950415478328469</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1268760488157937</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.06624779649780255</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2985680327635259</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.1877218494814678</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.1065659805960584</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.07894778572091943</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.05618041196635069</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.0610289771159607</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.02669430558489584</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.02727280396392601</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.04579211561353491</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1263481545309448</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.03393668819862264</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.06438617749876731</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.3381952468632087</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0.05804844341350592</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.1443268218410716</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.04497157109167603</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.03770764779211649</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-0.07336215883699738</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.0004625851260308695</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-0.00332711313939334</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.05477026807456952</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.2549445043088312</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0.08798292040722418</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.06555410588853898</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-0.1127933805848489</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.06581907123498155</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.02315264739475848</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>-0.1100519346446418</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.1180955924425124</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.0852131546994907</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>-0.1049272261330163</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.07645453878873093</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.01784764977311335</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.07429462373003233</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.02390465939149457</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>-0.04385257877989258</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>-0.03668736019321992</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.009703193031912196</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0.02130228817142515</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.1202110357146249</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.04051400407111189</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>-0.05010766021208047</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>-0.0532811408827087</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.04817032432922914</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.03122952291205565</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>-0.04077357990882677</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.0804063034873601</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0.05577014230257526</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>-0.1256583946542656</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.08299846685883565</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.007888313310900775</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>-0.04182426915310107</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.06327198353889837</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.007356698932015766</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.0005793672479718105</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.07186674441800714</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.004322962245330059</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>-0.1003264617589393</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.04136138386057726</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.465766274309512</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.221780018273259</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.3578978453844713</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.7199612890115109</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1066159931310041</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.3444712457022303</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.1510995607492166</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.1602895838538496</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.04067430392158198</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.01084772824398546</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.1584410531939759</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.1036103781682019</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.07875980137842389</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-0.01732311279838609</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.2593264589975018</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.835256724048108</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.05548334875304067</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.2225664678440765</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.1241380636831701</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.1112633399689659</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.2535635973502805</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.2288096614268567</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.2057519214211465</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.01487833486732031</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.4885170543280168</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.06122743971325487</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.214432386154963</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.1959418504857953</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.008755705554831433</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.1608818278928455</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.3777602045899002</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.1627410882436007</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.2565611708322482</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.2030059407804258</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.07038276829664893</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.1407107535488377</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>-0.02276676187672798</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>-0.1670184780668702</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>-0.03831472615290637</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.07121781940161186</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.006953772197448179</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.05140392469757582</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0.08708458333184345</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.04631369014937255</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.01238759435307514</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.02158093771242768</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.1682382372369848</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.03948089716227646</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>-0.01986852881293845</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>-0.1285272108104367</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.09904726896010797</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.2098599194239316</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.08550331609335353</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.1368559341908651</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.2510536975699814</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.1826168990689105</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>-0.2299660679968726</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.04275041441297692</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.001677724993393195</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.128965408346733</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.04820000553087018</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>-0.05778758596920687</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>-0.1942865770561278</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5971138735365376</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.1109927728534639</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.1786053943593191</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.8829827513174492</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.2357150449337614</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.07880778021703536</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.02124097694383537</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.3215498194856506</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.03877884734196532</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.0760442703594558</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>-0.2845703881712431</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.03711649595500979</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.1353964011447481</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.3367667521330294</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0.2207421027593831</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.4033479568850997</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>-0.3046051647580704</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.1898325266103745</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.2950651705579495</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.1883022024698196</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>-0.06678144357439865</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.1999549383817213</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.3337021975975376</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.001349664160165378</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.2782462440912766</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>-0.2119025224257297</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.09872387460347665</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>-0.1300915691884303</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.06957787516698918</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>-0.0654859191900098</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>-0.2988563658935294</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.02327201888441858</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.08738866647217369</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>-0.1719929969240856</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.03389661038080595</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>-0.006137197617644245</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>-0.04527050184407554</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>-0.1126009047217726</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.03857054772744926</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>-0.3034162335770083</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>-0.02421173614307401</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>-0.09771847409519847</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>-0.2018175015651081</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>-0.1634913369588808</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.03574744953116768</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.001984136190828946</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>-0.05624480857739249</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.03905860733547442</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>-0.02609218222937569</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.003321874411785894</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.1275123531238411</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>-0.1621360406185268</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.01791563494592071</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.02263472717877503</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>-0.1541201074590863</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>-0.01460385529673425</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0.002490503276954532</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.06824076108281009</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.05017352448565343</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.007484035517780419</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>-0.02786912322328429</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.4728590004560042</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.01597931183854157</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.2502667093820244</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.6097560569556197</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.1456274337525841</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-0.3016056378056466</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.159844346830544</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.09637763664563853</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.04082389461090154</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.07538345683315748</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.244190350783323</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.0560789379259061</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.1157677300065523</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.05970304219964365</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-0.06086454039009813</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.7312181516540841</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.2861219210266936</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0.2526580788142327</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.1396757029818096</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.04991787948180482</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>-0.04589489732528754</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.1240590990285246</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.04684571486874901</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>0.03971547426434927</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.4336584781234273</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.06795855090757856</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>-0.119017037861996</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.1556334192209373</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.04613366214792964</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.07129168629187371</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.2593265976979108</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.192955994430196</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.0358434112031945</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.1506335702139211</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.01934615198790359</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.1118664827044839</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.1083580600471234</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.1987985728552072</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.0451858445939847</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0.05679280293338675</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.02658633994577748</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>0.1090831846798762</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>-0.08264375263267858</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>-0.0166181156303015</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.02545754504592316</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.05506046931255109</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>-0.003621725438782805</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0.005974677100641339</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0.05172894385466301</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>-0.1008904303208177</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.003791924664288007</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.1809815123875899</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.005020711454437188</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.08899768555091409</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.1390783453488111</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>-0.0680567953704191</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.1587937051548156</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>-0.06048293068189721</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.09878973969974521</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>-0.1186198392295988</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>-0.04401819981408286</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.1581305790423395</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.1998487796028224</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.0314239007795144</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.0527406350295813</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.2382018156125356</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.07705437693923284</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.07252810611481193</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.05437181205990525</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.03615175363087817</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.000242601551310091</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.02794801894164767</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.1108792209998172</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.0255723571060595</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.009099735669900478</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.03365182154587251</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.004619318476316257</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.1965119146189816</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.1525261543582058</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>-0.09226245054064165</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>-0.01367101038677743</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.003036175754671663</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.002451489419600343</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.02571153998401499</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.0383298845189228</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-0.0001513168268013543</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.1109019828255924</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.03653187377922996</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-0.02626550833707703</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.04789010636263964</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.03178161295595747</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0.02035083335494526</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.04287301816410851</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.09857829928977198</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0.02423915725592221</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.04761244673519301</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.02418418556672424</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0.03244955989458749</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0.0285702736020394</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>-0.0522603213329171</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0.008366982534628701</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0.00304868630515343</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0.02674885433976575</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>-0.0002845509690470906</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>-0.0005077455469122673</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0.01476133231687698</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>-0.01504770884346118</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0.03103030016876016</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.02210794746048046</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0.00245771183234493</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>-0.01987157542311573</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0.01367985395678642</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0.04275820845945421</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0.05416269760446267</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.01792275938743833</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0.0164167272142652</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0.07176912416769286</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>-0.04739211653036215</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0.04738624800860768</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>-0.02038362734240499</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.03284979137489894</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>-0.03748450021534017</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>-0.04486083712585164</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0.03274023827819787</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
         <v>0</v>
       </c>
     </row>
